--- a/data/reports/report-2026-08-02.xlsx
+++ b/data/reports/report-2026-08-02.xlsx
@@ -33,8 +33,10 @@
     <sheet name="湯上がりワンピース" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="瞬間冷感ポンチョ" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="バランスケアスリッパ" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="カタログ全部" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="非広告商品" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="UVハット" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="車載ホルダー" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="カタログ全部" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="非広告商品" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'4WAY'!$A$13:$R$47</definedName>
@@ -56,6 +58,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="23" hidden="1">'湯上がりワンピース'!$A$13:$R$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="24" hidden="1">'瞬間冷感ポンチョ'!$A$13:$R$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="25" hidden="1">'バランスケアスリッパ'!$A$13:$R$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="26" hidden="1">'UVハット'!$A$13:$R$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="27" hidden="1">'車載ホルダー'!$A$13:$R$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38994,6 +38998,3514 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>完全遮光・接触冷感UVハット</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>売価 窓内で変動円 ／ 単価原価 1,411円 ／ 原価率(30日) 25.2% ／ 分岐MER 1.34 ／ 目標MER 2.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>※ 2026-07-31に新規出稿開始。同日に売価5,980→4,980円へ値下げしたため、販売数は日付に応じた売価で算出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>■ 期間サマリー</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>期間</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>売上</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>原価</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>広告費</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>利益</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>利益率</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>MER</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>余裕(MER−分岐)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>前日(08-01)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>19920</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>5644</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>6826</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>7450</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="G7" s="13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H7" s="13" t="n">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>3日(07-30-08-01)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>24900</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>7055</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>10016</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>7829</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="G8" s="13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H8" s="13" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>7日(07-26-08-01)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>24900</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>7055</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>10016</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>7829</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>30日(07-03-08-01)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>72740</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>18343</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>10016</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>44381</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>5.93</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>■ 日次</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>曜日指数</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>売上(gross−値引)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>値引</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>販売数</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>売価(実測)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>単価原価</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>原価</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>原価率</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>広告費</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>利益</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>利益率</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>MER</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>曜日補正MER</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>日予算</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>消化率</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr"/>
+      <c r="I14" s="10" t="n"/>
+      <c r="J14" s="12" t="inlineStr"/>
+      <c r="K14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12" t="inlineStr"/>
+      <c r="N14" s="13" t="inlineStr"/>
+      <c r="O14" s="13" t="inlineStr"/>
+      <c r="P14" s="10" t="inlineStr"/>
+      <c r="Q14" s="12" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H15" s="11" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I15" s="11" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J15" s="22" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M15" s="22" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N15" s="24" t="inlineStr"/>
+      <c r="O15" s="24" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr"/>
+      <c r="Q15" s="22" t="inlineStr"/>
+      <c r="R15" s="25" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="n"/>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12" t="inlineStr"/>
+      <c r="N16" s="13" t="inlineStr"/>
+      <c r="O16" s="13" t="inlineStr"/>
+      <c r="P16" s="10" t="inlineStr"/>
+      <c r="Q16" s="12" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>96</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="21" t="n"/>
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="22" t="inlineStr"/>
+      <c r="K17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="22" t="inlineStr"/>
+      <c r="N17" s="24" t="inlineStr"/>
+      <c r="O17" s="24" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr"/>
+      <c r="Q17" s="22" t="inlineStr"/>
+      <c r="R17" s="25" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr"/>
+      <c r="I18" s="10" t="n"/>
+      <c r="J18" s="12" t="inlineStr"/>
+      <c r="K18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12" t="inlineStr"/>
+      <c r="N18" s="13" t="inlineStr"/>
+      <c r="O18" s="13" t="inlineStr"/>
+      <c r="P18" s="10" t="inlineStr"/>
+      <c r="Q18" s="12" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="21" t="n"/>
+      <c r="G19" s="11" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="22" t="inlineStr"/>
+      <c r="K19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="22" t="inlineStr"/>
+      <c r="N19" s="24" t="inlineStr"/>
+      <c r="O19" s="24" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr"/>
+      <c r="Q19" s="22" t="inlineStr"/>
+      <c r="R19" s="25" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I20" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J20" s="12" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M20" s="12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N20" s="13" t="inlineStr"/>
+      <c r="O20" s="13" t="inlineStr"/>
+      <c r="P20" s="10" t="inlineStr"/>
+      <c r="Q20" s="12" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="21" t="n"/>
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="22" t="inlineStr"/>
+      <c r="K21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="22" t="inlineStr"/>
+      <c r="N21" s="24" t="inlineStr"/>
+      <c r="O21" s="24" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr"/>
+      <c r="Q21" s="22" t="inlineStr"/>
+      <c r="R21" s="25" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="12" t="inlineStr"/>
+      <c r="K22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12" t="inlineStr"/>
+      <c r="N22" s="13" t="inlineStr"/>
+      <c r="O22" s="13" t="inlineStr"/>
+      <c r="P22" s="10" t="inlineStr"/>
+      <c r="Q22" s="12" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J23" s="22" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M23" s="22" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N23" s="24" t="inlineStr"/>
+      <c r="O23" s="24" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr"/>
+      <c r="Q23" s="22" t="inlineStr"/>
+      <c r="R23" s="25" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I24" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J24" s="12" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M24" s="12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N24" s="13" t="inlineStr"/>
+      <c r="O24" s="13" t="inlineStr"/>
+      <c r="P24" s="10" t="inlineStr"/>
+      <c r="Q24" s="12" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="21" t="n"/>
+      <c r="G25" s="11" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="22" t="inlineStr"/>
+      <c r="K25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="22" t="inlineStr"/>
+      <c r="N25" s="24" t="inlineStr"/>
+      <c r="O25" s="24" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr"/>
+      <c r="Q25" s="22" t="inlineStr"/>
+      <c r="R25" s="25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M26" s="12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N26" s="13" t="inlineStr"/>
+      <c r="O26" s="13" t="inlineStr"/>
+      <c r="P26" s="10" t="inlineStr"/>
+      <c r="Q26" s="12" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="21" t="n"/>
+      <c r="G27" s="11" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="22" t="inlineStr"/>
+      <c r="K27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="22" t="inlineStr"/>
+      <c r="N27" s="24" t="inlineStr"/>
+      <c r="O27" s="24" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr"/>
+      <c r="Q27" s="22" t="inlineStr"/>
+      <c r="R27" s="25" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I28" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J28" s="12" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr"/>
+      <c r="P28" s="10" t="inlineStr"/>
+      <c r="Q28" s="12" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="21" t="n"/>
+      <c r="G29" s="11" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="22" t="inlineStr"/>
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="22" t="inlineStr"/>
+      <c r="N29" s="24" t="inlineStr"/>
+      <c r="O29" s="24" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr"/>
+      <c r="Q29" s="22" t="inlineStr"/>
+      <c r="R29" s="25" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M30" s="12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N30" s="13" t="inlineStr"/>
+      <c r="O30" s="13" t="inlineStr"/>
+      <c r="P30" s="10" t="inlineStr"/>
+      <c r="Q30" s="12" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>96</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="21" t="n"/>
+      <c r="G31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="22" t="inlineStr"/>
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="22" t="inlineStr"/>
+      <c r="N31" s="24" t="inlineStr"/>
+      <c r="O31" s="24" t="inlineStr"/>
+      <c r="P31" s="11" t="inlineStr"/>
+      <c r="Q31" s="22" t="inlineStr"/>
+      <c r="R31" s="25" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="n"/>
+      <c r="J32" s="12" t="inlineStr"/>
+      <c r="K32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="12" t="inlineStr"/>
+      <c r="N32" s="13" t="inlineStr"/>
+      <c r="O32" s="13" t="inlineStr"/>
+      <c r="P32" s="10" t="inlineStr"/>
+      <c r="Q32" s="12" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="21" t="n"/>
+      <c r="G33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="22" t="inlineStr"/>
+      <c r="K33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="22" t="inlineStr"/>
+      <c r="N33" s="24" t="inlineStr"/>
+      <c r="O33" s="24" t="inlineStr"/>
+      <c r="P33" s="11" t="inlineStr"/>
+      <c r="Q33" s="22" t="inlineStr"/>
+      <c r="R33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="10" t="inlineStr"/>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="n"/>
+      <c r="J34" s="12" t="inlineStr"/>
+      <c r="K34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="inlineStr"/>
+      <c r="N34" s="13" t="inlineStr"/>
+      <c r="O34" s="13" t="inlineStr"/>
+      <c r="P34" s="10" t="inlineStr"/>
+      <c r="Q34" s="12" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H35" s="11" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I35" s="11" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J35" s="22" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M35" s="22" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N35" s="24" t="inlineStr"/>
+      <c r="O35" s="24" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
+      <c r="Q35" s="22" t="inlineStr"/>
+      <c r="R35" s="36" t="inlineStr">
+        <is>
+          <t>祝日(海の日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="12" t="inlineStr"/>
+      <c r="K36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12" t="inlineStr"/>
+      <c r="N36" s="13" t="inlineStr"/>
+      <c r="O36" s="13" t="inlineStr"/>
+      <c r="P36" s="10" t="inlineStr"/>
+      <c r="Q36" s="12" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="21" t="n"/>
+      <c r="G37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="n"/>
+      <c r="J37" s="22" t="inlineStr"/>
+      <c r="K37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="22" t="inlineStr"/>
+      <c r="N37" s="24" t="inlineStr"/>
+      <c r="O37" s="24" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
+      <c r="Q37" s="22" t="inlineStr"/>
+      <c r="R37" s="25" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I38" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J38" s="12" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>4569</v>
+      </c>
+      <c r="M38" s="12" t="n">
+        <v>0.764</v>
+      </c>
+      <c r="N38" s="13" t="inlineStr"/>
+      <c r="O38" s="13" t="inlineStr"/>
+      <c r="P38" s="10" t="inlineStr"/>
+      <c r="Q38" s="12" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="21" t="n"/>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="22" t="inlineStr"/>
+      <c r="K39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="22" t="inlineStr"/>
+      <c r="N39" s="24" t="inlineStr"/>
+      <c r="O39" s="24" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="22" t="inlineStr"/>
+      <c r="R39" s="25" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="12" t="inlineStr"/>
+      <c r="K40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="12" t="inlineStr"/>
+      <c r="N40" s="13" t="inlineStr"/>
+      <c r="O40" s="13" t="inlineStr"/>
+      <c r="P40" s="10" t="inlineStr"/>
+      <c r="Q40" s="12" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="21" t="n"/>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="22" t="inlineStr"/>
+      <c r="K41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="22" t="inlineStr"/>
+      <c r="N41" s="24" t="inlineStr"/>
+      <c r="O41" s="24" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr"/>
+      <c r="Q41" s="22" t="inlineStr"/>
+      <c r="R41" s="25" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="12" t="inlineStr"/>
+      <c r="K42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="12" t="inlineStr"/>
+      <c r="N42" s="13" t="inlineStr"/>
+      <c r="O42" s="13" t="inlineStr"/>
+      <c r="P42" s="10" t="inlineStr"/>
+      <c r="Q42" s="12" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="21" t="n"/>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="22" t="inlineStr"/>
+      <c r="K43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="22" t="inlineStr"/>
+      <c r="N43" s="24" t="inlineStr"/>
+      <c r="O43" s="24" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr"/>
+      <c r="Q43" s="22" t="inlineStr"/>
+      <c r="R43" s="25" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="12" t="inlineStr"/>
+      <c r="K44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="12" t="inlineStr"/>
+      <c r="N44" s="13" t="inlineStr"/>
+      <c r="O44" s="13" t="inlineStr"/>
+      <c r="P44" s="10" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>96</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="21" t="n"/>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="22" t="inlineStr"/>
+      <c r="K45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="22" t="inlineStr"/>
+      <c r="N45" s="24" t="inlineStr"/>
+      <c r="O45" s="24" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr"/>
+      <c r="Q45" s="22" t="inlineStr"/>
+      <c r="R45" s="25" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>4980</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>4980</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="K46" s="10" t="n">
+        <v>3190</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>379</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>0.0761</v>
+      </c>
+      <c r="N46" s="31" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P46" s="10" t="inlineStr"/>
+      <c r="Q46" s="12" t="inlineStr"/>
+      <c r="R46" s="36" t="inlineStr">
+        <is>
+          <t>新規出稿開始（日予算8,000）＋売価 5,980→4,980へ値下げ</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>19920</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>4980</v>
+      </c>
+      <c r="H47" s="11" t="n">
+        <v>1411</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>5644</v>
+      </c>
+      <c r="J47" s="22" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="K47" s="11" t="n">
+        <v>6826</v>
+      </c>
+      <c r="L47" s="11" t="n">
+        <v>7450</v>
+      </c>
+      <c r="M47" s="22" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="N47" s="23" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O47" s="24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="P47" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Q47" s="22" t="n">
+        <v>0.853</v>
+      </c>
+      <c r="R47" s="25" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A13:R47"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>W固定スマホ車載ホルダー</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>売価 3980円 ／ 単価原価 1,182円 ／ 原価率(定価ベース) 29.7% ／ 分岐MER 1.42 ／ 目標MER 2.83 ※30日窓に売上がないため実測比率ではなく定価から算出</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>※ 2026-08-01に新規出稿開始（通年商品）。売価3,980円・原価1,182円・原価率29.7%・分岐CPA2,798円・分岐MER1.42・目標MER2.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>■ 期間サマリー</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>期間</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>売上</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>原価</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>広告費</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>利益</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>利益率</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>MER</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>余裕(MER−分岐)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>前日(08-01)</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>2363</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="38" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>3日(07-30-08-01)</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>2363</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>7日(07-26-08-01)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>2363</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="38" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>30日(07-03-08-01)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>2363</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="F10" s="12" t="inlineStr"/>
+      <c r="G10" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="38" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>■ 日次</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>曜日</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>曜日指数</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>売上(gross−値引)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>値引</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>販売数</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>売価(実測)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>単価原価</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>原価</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>原価率</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>広告費</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>利益</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>利益率</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>MER</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>曜日補正MER</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>日予算</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>消化率</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>メモ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr"/>
+      <c r="I14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="12" t="inlineStr"/>
+      <c r="K14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="12" t="inlineStr"/>
+      <c r="N14" s="13" t="inlineStr"/>
+      <c r="O14" s="13" t="inlineStr"/>
+      <c r="P14" s="10" t="inlineStr"/>
+      <c r="Q14" s="12" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="22" t="inlineStr"/>
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="22" t="inlineStr"/>
+      <c r="N15" s="24" t="inlineStr"/>
+      <c r="O15" s="24" t="inlineStr"/>
+      <c r="P15" s="11" t="inlineStr"/>
+      <c r="Q15" s="22" t="inlineStr"/>
+      <c r="R15" s="25" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="10" t="inlineStr"/>
+      <c r="H16" s="10" t="inlineStr"/>
+      <c r="I16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="12" t="inlineStr"/>
+      <c r="K16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="12" t="inlineStr"/>
+      <c r="N16" s="13" t="inlineStr"/>
+      <c r="O16" s="13" t="inlineStr"/>
+      <c r="P16" s="10" t="inlineStr"/>
+      <c r="Q16" s="12" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="n">
+        <v>96</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="11" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr"/>
+      <c r="I17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="22" t="inlineStr"/>
+      <c r="K17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="22" t="inlineStr"/>
+      <c r="N17" s="24" t="inlineStr"/>
+      <c r="O17" s="24" t="inlineStr"/>
+      <c r="P17" s="11" t="inlineStr"/>
+      <c r="Q17" s="22" t="inlineStr"/>
+      <c r="R17" s="25" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="10" t="inlineStr"/>
+      <c r="H18" s="10" t="inlineStr"/>
+      <c r="I18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="12" t="inlineStr"/>
+      <c r="K18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="12" t="inlineStr"/>
+      <c r="N18" s="13" t="inlineStr"/>
+      <c r="O18" s="13" t="inlineStr"/>
+      <c r="P18" s="10" t="inlineStr"/>
+      <c r="Q18" s="12" t="inlineStr"/>
+      <c r="R18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="22" t="inlineStr"/>
+      <c r="K19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="22" t="inlineStr"/>
+      <c r="N19" s="24" t="inlineStr"/>
+      <c r="O19" s="24" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr"/>
+      <c r="Q19" s="22" t="inlineStr"/>
+      <c r="R19" s="25" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12" t="inlineStr"/>
+      <c r="K20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="12" t="inlineStr"/>
+      <c r="N20" s="13" t="inlineStr"/>
+      <c r="O20" s="13" t="inlineStr"/>
+      <c r="P20" s="10" t="inlineStr"/>
+      <c r="Q20" s="12" t="inlineStr"/>
+      <c r="R20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="22" t="inlineStr"/>
+      <c r="K21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="22" t="inlineStr"/>
+      <c r="N21" s="24" t="inlineStr"/>
+      <c r="O21" s="24" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr"/>
+      <c r="Q21" s="22" t="inlineStr"/>
+      <c r="R21" s="25" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="12" t="inlineStr"/>
+      <c r="K22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="12" t="inlineStr"/>
+      <c r="N22" s="13" t="inlineStr"/>
+      <c r="O22" s="13" t="inlineStr"/>
+      <c r="P22" s="10" t="inlineStr"/>
+      <c r="Q22" s="12" t="inlineStr"/>
+      <c r="R22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr"/>
+      <c r="I23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="22" t="inlineStr"/>
+      <c r="K23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="22" t="inlineStr"/>
+      <c r="N23" s="24" t="inlineStr"/>
+      <c r="O23" s="24" t="inlineStr"/>
+      <c r="P23" s="11" t="inlineStr"/>
+      <c r="Q23" s="22" t="inlineStr"/>
+      <c r="R23" s="25" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="inlineStr"/>
+      <c r="K24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="12" t="inlineStr"/>
+      <c r="N24" s="13" t="inlineStr"/>
+      <c r="O24" s="13" t="inlineStr"/>
+      <c r="P24" s="10" t="inlineStr"/>
+      <c r="Q24" s="12" t="inlineStr"/>
+      <c r="R24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="11" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="22" t="inlineStr"/>
+      <c r="K25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="22" t="inlineStr"/>
+      <c r="N25" s="24" t="inlineStr"/>
+      <c r="O25" s="24" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr"/>
+      <c r="Q25" s="22" t="inlineStr"/>
+      <c r="R25" s="25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="10" t="inlineStr"/>
+      <c r="H26" s="10" t="inlineStr"/>
+      <c r="I26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="inlineStr"/>
+      <c r="K26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="12" t="inlineStr"/>
+      <c r="N26" s="13" t="inlineStr"/>
+      <c r="O26" s="13" t="inlineStr"/>
+      <c r="P26" s="10" t="inlineStr"/>
+      <c r="Q26" s="12" t="inlineStr"/>
+      <c r="R26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="11" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="22" t="inlineStr"/>
+      <c r="K27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="22" t="inlineStr"/>
+      <c r="N27" s="24" t="inlineStr"/>
+      <c r="O27" s="24" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr"/>
+      <c r="Q27" s="22" t="inlineStr"/>
+      <c r="R27" s="25" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="10" t="inlineStr"/>
+      <c r="H28" s="10" t="inlineStr"/>
+      <c r="I28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="inlineStr"/>
+      <c r="K28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="12" t="inlineStr"/>
+      <c r="N28" s="13" t="inlineStr"/>
+      <c r="O28" s="13" t="inlineStr"/>
+      <c r="P28" s="10" t="inlineStr"/>
+      <c r="Q28" s="12" t="inlineStr"/>
+      <c r="R28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="22" t="inlineStr"/>
+      <c r="K29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="22" t="inlineStr"/>
+      <c r="N29" s="24" t="inlineStr"/>
+      <c r="O29" s="24" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr"/>
+      <c r="Q29" s="22" t="inlineStr"/>
+      <c r="R29" s="25" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="10" t="inlineStr"/>
+      <c r="H30" s="10" t="inlineStr"/>
+      <c r="I30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="12" t="inlineStr"/>
+      <c r="K30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="12" t="inlineStr"/>
+      <c r="N30" s="13" t="inlineStr"/>
+      <c r="O30" s="13" t="inlineStr"/>
+      <c r="P30" s="10" t="inlineStr"/>
+      <c r="Q30" s="12" t="inlineStr"/>
+      <c r="R30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="n">
+        <v>96</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr"/>
+      <c r="I31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="22" t="inlineStr"/>
+      <c r="K31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="22" t="inlineStr"/>
+      <c r="N31" s="24" t="inlineStr"/>
+      <c r="O31" s="24" t="inlineStr"/>
+      <c r="P31" s="11" t="inlineStr"/>
+      <c r="Q31" s="22" t="inlineStr"/>
+      <c r="R31" s="25" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
+      <c r="I32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="12" t="inlineStr"/>
+      <c r="K32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="12" t="inlineStr"/>
+      <c r="N32" s="13" t="inlineStr"/>
+      <c r="O32" s="13" t="inlineStr"/>
+      <c r="P32" s="10" t="inlineStr"/>
+      <c r="Q32" s="12" t="inlineStr"/>
+      <c r="R32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="22" t="inlineStr"/>
+      <c r="K33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="22" t="inlineStr"/>
+      <c r="N33" s="24" t="inlineStr"/>
+      <c r="O33" s="24" t="inlineStr"/>
+      <c r="P33" s="11" t="inlineStr"/>
+      <c r="Q33" s="22" t="inlineStr"/>
+      <c r="R33" s="25" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="10" t="inlineStr"/>
+      <c r="H34" s="10" t="inlineStr"/>
+      <c r="I34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="12" t="inlineStr"/>
+      <c r="K34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="12" t="inlineStr"/>
+      <c r="N34" s="13" t="inlineStr"/>
+      <c r="O34" s="13" t="inlineStr"/>
+      <c r="P34" s="10" t="inlineStr"/>
+      <c r="Q34" s="12" t="inlineStr"/>
+      <c r="R34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="34" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="11" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="22" t="inlineStr"/>
+      <c r="K35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="22" t="inlineStr"/>
+      <c r="N35" s="24" t="inlineStr"/>
+      <c r="O35" s="24" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
+      <c r="Q35" s="22" t="inlineStr"/>
+      <c r="R35" s="36" t="inlineStr">
+        <is>
+          <t>祝日(海の日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="10" t="inlineStr"/>
+      <c r="H36" s="10" t="inlineStr"/>
+      <c r="I36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="12" t="inlineStr"/>
+      <c r="K36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="12" t="inlineStr"/>
+      <c r="N36" s="13" t="inlineStr"/>
+      <c r="O36" s="13" t="inlineStr"/>
+      <c r="P36" s="10" t="inlineStr"/>
+      <c r="Q36" s="12" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B37" s="21" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="22" t="inlineStr"/>
+      <c r="K37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="22" t="inlineStr"/>
+      <c r="N37" s="24" t="inlineStr"/>
+      <c r="O37" s="24" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
+      <c r="Q37" s="22" t="inlineStr"/>
+      <c r="R37" s="25" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="10" t="inlineStr"/>
+      <c r="H38" s="10" t="inlineStr"/>
+      <c r="I38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="12" t="inlineStr"/>
+      <c r="K38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="12" t="inlineStr"/>
+      <c r="N38" s="13" t="inlineStr"/>
+      <c r="O38" s="13" t="inlineStr"/>
+      <c r="P38" s="10" t="inlineStr"/>
+      <c r="Q38" s="12" t="inlineStr"/>
+      <c r="R38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
+      <c r="I39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="22" t="inlineStr"/>
+      <c r="K39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="22" t="inlineStr"/>
+      <c r="N39" s="24" t="inlineStr"/>
+      <c r="O39" s="24" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="22" t="inlineStr"/>
+      <c r="R39" s="25" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="10" t="inlineStr"/>
+      <c r="H40" s="10" t="inlineStr"/>
+      <c r="I40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="12" t="inlineStr"/>
+      <c r="K40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="12" t="inlineStr"/>
+      <c r="N40" s="13" t="inlineStr"/>
+      <c r="O40" s="13" t="inlineStr"/>
+      <c r="P40" s="10" t="inlineStr"/>
+      <c r="Q40" s="12" t="inlineStr"/>
+      <c r="R40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B41" s="21" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="22" t="inlineStr"/>
+      <c r="K41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="22" t="inlineStr"/>
+      <c r="N41" s="24" t="inlineStr"/>
+      <c r="O41" s="24" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr"/>
+      <c r="Q41" s="22" t="inlineStr"/>
+      <c r="R41" s="25" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C42" s="13" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="10" t="inlineStr"/>
+      <c r="H42" s="10" t="inlineStr"/>
+      <c r="I42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" s="12" t="inlineStr"/>
+      <c r="K42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="12" t="inlineStr"/>
+      <c r="N42" s="13" t="inlineStr"/>
+      <c r="O42" s="13" t="inlineStr"/>
+      <c r="P42" s="10" t="inlineStr"/>
+      <c r="Q42" s="12" t="inlineStr"/>
+      <c r="R42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B43" s="21" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="22" t="inlineStr"/>
+      <c r="K43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="22" t="inlineStr"/>
+      <c r="N43" s="24" t="inlineStr"/>
+      <c r="O43" s="24" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr"/>
+      <c r="Q43" s="22" t="inlineStr"/>
+      <c r="R43" s="25" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C44" s="13" t="n">
+        <v>104.1</v>
+      </c>
+      <c r="D44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="10" t="inlineStr"/>
+      <c r="H44" s="10" t="inlineStr"/>
+      <c r="I44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="12" t="inlineStr"/>
+      <c r="K44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="12" t="inlineStr"/>
+      <c r="N44" s="13" t="inlineStr"/>
+      <c r="O44" s="13" t="inlineStr"/>
+      <c r="P44" s="10" t="inlineStr"/>
+      <c r="Q44" s="12" t="inlineStr"/>
+      <c r="R44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>96</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
+      <c r="I45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="22" t="inlineStr"/>
+      <c r="K45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="22" t="inlineStr"/>
+      <c r="N45" s="24" t="inlineStr"/>
+      <c r="O45" s="24" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr"/>
+      <c r="Q45" s="22" t="inlineStr"/>
+      <c r="R45" s="25" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="10" t="inlineStr"/>
+      <c r="H46" s="10" t="inlineStr"/>
+      <c r="I46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="12" t="inlineStr"/>
+      <c r="K46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="12" t="inlineStr"/>
+      <c r="N46" s="13" t="inlineStr"/>
+      <c r="O46" s="13" t="inlineStr"/>
+      <c r="P46" s="10" t="inlineStr"/>
+      <c r="Q46" s="12" t="inlineStr"/>
+      <c r="R46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="inlineStr">
+        <is>
+          <t>土</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="n">
+        <v>103.2</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="11" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="22" t="inlineStr"/>
+      <c r="K47" s="11" t="n">
+        <v>2363</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="M47" s="22" t="inlineStr"/>
+      <c r="N47" s="24" t="inlineStr"/>
+      <c r="O47" s="24" t="inlineStr"/>
+      <c r="P47" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Q47" s="22" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="R47" s="36" t="inlineStr">
+        <is>
+          <t>⚠️消化率が異常（当日中の予算変更 or 開始初日 or スナップショット欠落を確認） ／ 新規出稿開始（日予算8,000・分岐CPA2,798円・通年商品）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A13:R47"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -39688,331 +43200,6 @@
       </c>
       <c r="E39" s="12" t="n">
         <v>1.097</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>広告を出していない商品（広告費0円。利益＝売上−原価）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>商品</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>売価</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>単価原価</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>30日売上</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>30日販売数</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>30日原価</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>30日利益</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>30日利益率</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>優先配送</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="n">
-        <v>536</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10" t="n">
-        <v>141504</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>264</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="10" t="n">
-        <v>141504</v>
-      </c>
-      <c r="H4" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>瞬間冷却ハンディファン</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="C5" s="10" t="n">
-        <v>2053</v>
-      </c>
-      <c r="D5" s="10" t="n">
-        <v>110032</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>39007</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>71025</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.6455</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>完全遮光・接触冷感UVハット</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="C6" s="10" t="n">
-        <v>1411</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>78720</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>18343</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>60377</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.767</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>ナノバブルシャワーヘッド</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>6980</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>2255</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>55840</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>18040</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <v>37800</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.6768999999999999</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>リカバリーサンダル</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>3980</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>1309</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>31840</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>8</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>10472</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>21368</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.6711</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>ネックマッサージャー</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>9980</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>3034</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>9980</v>
-      </c>
-      <c r="E9" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>3034</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>6946</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.696</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>姿勢サポートベルト</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>1429</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>1429</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>4551</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>0.761</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>癒しの指圧マット</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>1648</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>1648</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>4332</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0.7244</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>スマートノーズEMS美顔器</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>変動</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>5980</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -40722,6 +43909,303 @@
         <is>
           <t>・MER・分岐MER・目標MER・増分MERはすべて手数料控除前で統一。</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>広告を出していない商品（広告費0円。利益＝売上−原価）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>商品</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>売価</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>単価原価</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>30日売上</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>30日販売数</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>30日原価</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>30日利益</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>30日利益率</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>優先配送</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>536</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>141504</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>264</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>141504</v>
+      </c>
+      <c r="H4" s="12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>瞬間冷却ハンディファン</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>2053</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>110032</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>39007</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>71025</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.6455</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>ナノバブルシャワーヘッド</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>6980</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>2255</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>55840</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>18040</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>37800</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>リカバリーサンダル</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>3980</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>1309</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>31840</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>10472</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>21368</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.6711</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>ネックマッサージャー</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>9980</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>3034</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>9980</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>3034</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>6946</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>0.696</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>姿勢サポートベルト</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1429</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1429</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>4551</v>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>0.761</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>癒しの指圧マット</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>1648</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>1648</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>4332</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.7244</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>スマートノーズEMS美顔器</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>変動</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>5980</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -45149,7 +48633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -46385,6 +49869,122 @@
       </c>
       <c r="R24" s="10" t="n">
         <v>5000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>完全遮光・接触冷感UVハット</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>変動</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>1411</v>
+      </c>
+      <c r="D25" s="12" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>72740</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>18343</v>
+      </c>
+      <c r="I25" s="10" t="n">
+        <v>10016</v>
+      </c>
+      <c r="J25" s="10" t="n">
+        <v>44381</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>0.6101</v>
+      </c>
+      <c r="L25" s="23" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="M25" s="10" t="n">
+        <v>24900</v>
+      </c>
+      <c r="N25" s="10" t="n">
+        <v>10016</v>
+      </c>
+      <c r="O25" s="10" t="n">
+        <v>7829</v>
+      </c>
+      <c r="P25" s="13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="Q25" s="10" t="n">
+        <v>7450</v>
+      </c>
+      <c r="R25" s="10" t="n">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>W固定スマホ車載ホルダー</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>3980</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>1182</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10" t="n">
+        <v>2363</v>
+      </c>
+      <c r="J26" s="28" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="K26" s="12" t="inlineStr"/>
+      <c r="L26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="10" t="n">
+        <v>2363</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="P26" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="28" t="n">
+        <v>-2363</v>
+      </c>
+      <c r="R26" s="10" t="n">
+        <v>8000</v>
       </c>
     </row>
   </sheetData>
@@ -50840,7 +54440,7 @@
       </c>
       <c r="R47" s="36" t="inlineStr">
         <is>
-          <t>日予算 72,000→55,000円</t>
+          <t>日予算 72,000→55,000円 ／ 本体セット減額 60,000→43,000</t>
         </is>
       </c>
     </row>
